--- a/Marketing_Performance.xlsx
+++ b/Marketing_Performance.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\Marketing_Performance_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2FD18DD-C695-4525-94AB-DF6033959486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F47C932-5CB8-41DB-875E-EAF25B7E789B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D3142753-8123-445A-ADEA-4B38D5A12F31}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="14">
   <si>
     <t>Quarter</t>
   </si>
@@ -71,25 +71,22 @@
     <t>TCPL</t>
   </si>
   <si>
-    <t>Q1</t>
+    <t>Q1'26</t>
   </si>
   <si>
-    <t>Q2</t>
+    <t>Q2'26</t>
   </si>
   <si>
-    <t>Q3</t>
+    <t>Q3'26</t>
   </si>
   <si>
-    <t>Q4</t>
+    <t>Q4'26</t>
   </si>
   <si>
-    <t>Apr'26</t>
+    <t>Q1'27</t>
   </si>
   <si>
-    <t>May'26</t>
-  </si>
-  <si>
-    <t>Jun'26</t>
+    <t>July'26</t>
   </si>
 </sst>
 </file>
@@ -134,7 +131,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -181,25 +178,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -220,14 +204,9 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -563,10 +542,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A677B399-AC58-451E-981E-A5DCEA21A9CB}">
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.81640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.81640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.81640625" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="9.90625" bestFit="1" customWidth="1"/>
@@ -613,7 +593,7 @@
         <v>79436651.003333345</v>
       </c>
       <c r="D3" s="2">
-        <f t="shared" ref="D3:D8" si="0">1-B3/C3</f>
+        <f t="shared" ref="D3:D7" si="0">1-B3/C3</f>
         <v>0.67291085405598183</v>
       </c>
       <c r="I3" s="1"/>
@@ -652,72 +632,55 @@
       </c>
       <c r="I5" s="6"/>
       <c r="J5" s="8"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>12</v>
       </c>
       <c r="B6">
-        <v>20494611</v>
+        <v>21575648.999999996</v>
       </c>
       <c r="C6">
-        <v>62670342</v>
+        <v>65128639</v>
       </c>
       <c r="D6" s="2">
         <f t="shared" si="0"/>
-        <v>0.67297751462725386</v>
-      </c>
-      <c r="I6" s="6"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
+        <v>0.66872255690772231</v>
+      </c>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>13</v>
       </c>
       <c r="B7">
-        <v>22716933</v>
+        <v>24481433</v>
       </c>
       <c r="C7">
-        <v>64088288</v>
+        <v>74223589.170000002</v>
       </c>
       <c r="D7" s="2">
         <f t="shared" si="0"/>
-        <v>0.64553690371632333</v>
-      </c>
-      <c r="I7" s="6"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8">
-        <v>19698853</v>
-      </c>
-      <c r="C8">
-        <v>20670650</v>
-      </c>
-      <c r="D8" s="2">
-        <f t="shared" si="0"/>
-        <v>4.7013374035165811E-2</v>
-      </c>
-      <c r="I8" s="6"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
+        <v>0.67016640836475472</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="I9" s="1"/>
+      <c r="I9" s="2"/>
       <c r="J9" s="1"/>
     </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+    </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="I12" s="2"/>
+      <c r="I12" s="1"/>
       <c r="J12" s="1"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
@@ -731,18 +694,6 @@
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-    </row>
-    <row r="17" spans="9:10" x14ac:dyDescent="0.35">
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-    </row>
-    <row r="18" spans="9:10" x14ac:dyDescent="0.35">
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -751,10 +702,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46C76C1D-CCBC-4BF0-AA51-263FDCFF00F6}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="3" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
@@ -823,7 +775,7 @@
         <v>30661397</v>
       </c>
       <c r="D3" s="2">
-        <f t="shared" ref="D3:D8" si="0">IFERROR(1-B3/C3,)</f>
+        <f t="shared" ref="D3:D5" si="0">IFERROR(1-B3/C3,)</f>
         <v>0.67548190971207211</v>
       </c>
       <c r="E3" s="1">
@@ -833,11 +785,11 @@
         <v>168120</v>
       </c>
       <c r="G3" s="3">
-        <f t="shared" ref="G3:G8" si="1">IFERROR(B3/E3,)</f>
+        <f t="shared" ref="G3:G5" si="1">IFERROR(B3/E3,)</f>
         <v>34.611842952006931</v>
       </c>
       <c r="H3" s="3">
-        <f t="shared" ref="H3:H8" si="2">IFERROR(B3/F3,)</f>
+        <f t="shared" ref="H3:H5" si="2">IFERROR(B3/F3,)</f>
         <v>59.184975017844394</v>
       </c>
     </row>
@@ -904,28 +856,27 @@
         <v>12</v>
       </c>
       <c r="B6" s="1">
-        <v>7043335</v>
+        <v>7113673.666666667</v>
       </c>
       <c r="C6" s="1">
-        <v>20108993</v>
+        <v>20015488.666666668</v>
       </c>
       <c r="D6" s="2">
-        <f t="shared" si="0"/>
-        <v>0.64974203332807368</v>
+        <v>0.64459155681201952</v>
       </c>
       <c r="E6" s="1">
-        <v>203982</v>
+        <v>209356.33333333334</v>
       </c>
       <c r="F6" s="1">
-        <v>121423</v>
+        <v>118740.66666666667</v>
       </c>
       <c r="G6" s="3">
-        <f t="shared" si="1"/>
-        <v>34.529198654783265</v>
+        <f t="shared" ref="G6:G7" si="3">IFERROR(B6/E6,)</f>
+        <v>33.978784178171509</v>
       </c>
       <c r="H6" s="3">
-        <f t="shared" si="2"/>
-        <v>58.006596773263716</v>
+        <f t="shared" ref="H6:H7" si="4">IFERROR(B6/F6,)</f>
+        <v>59.909329013929515</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -933,57 +884,27 @@
         <v>13</v>
       </c>
       <c r="B7" s="1">
-        <v>7345395</v>
+        <v>8926903</v>
       </c>
       <c r="C7" s="1">
-        <v>20039034</v>
+        <v>23335174.170000002</v>
       </c>
       <c r="D7" s="2">
-        <f t="shared" si="0"/>
-        <v>0.63344565411686005</v>
+        <v>0.64459155681201952</v>
       </c>
       <c r="E7" s="1">
-        <v>214425</v>
+        <v>195079</v>
       </c>
       <c r="F7" s="1">
-        <v>124417</v>
+        <v>131897</v>
       </c>
       <c r="G7" s="3">
-        <f t="shared" si="1"/>
-        <v>34.256243441762855</v>
+        <f t="shared" si="3"/>
+        <v>45.760450894253097</v>
       </c>
       <c r="H7" s="3">
-        <f t="shared" si="2"/>
-        <v>59.038515636930647</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="1">
-        <v>6094299</v>
-      </c>
-      <c r="C8" s="1">
-        <v>16856556</v>
-      </c>
-      <c r="D8" s="2">
-        <f t="shared" si="0"/>
-        <v>0.63846120168319076</v>
-      </c>
-      <c r="E8" s="1">
-        <v>161488</v>
-      </c>
-      <c r="F8" s="1">
-        <v>95572</v>
-      </c>
-      <c r="G8" s="3">
-        <f t="shared" si="1"/>
-        <v>37.738401614980681</v>
-      </c>
-      <c r="H8" s="3">
-        <f t="shared" si="2"/>
-        <v>63.766573891934875</v>
+        <f t="shared" si="4"/>
+        <v>67.680864614054911</v>
       </c>
     </row>
   </sheetData>
@@ -994,7 +915,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F030C1A-8917-4C2A-88A6-06DD1C3DF39B}">
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="3" width="12.453125" bestFit="1" customWidth="1"/>
@@ -1005,7 +926,7 @@
     <col min="10" max="10" width="11.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1031,7 +952,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1060,7 +981,7 @@
         <v>102.71389190223981</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1071,7 +992,7 @@
         <v>20252592</v>
       </c>
       <c r="D3" s="2">
-        <f t="shared" ref="D3:D8" si="0">IFERROR(1-B3/C3,)</f>
+        <f t="shared" ref="D3:D7" si="0">IFERROR(1-B3/C3,)</f>
         <v>0.65806801420776173</v>
       </c>
       <c r="E3" s="1">
@@ -1081,15 +1002,15 @@
         <v>82175</v>
       </c>
       <c r="G3" s="3">
-        <f t="shared" ref="G3:G8" si="1">IFERROR(B3/E3,)</f>
+        <f t="shared" ref="G3:G5" si="1">IFERROR(B3/E3,)</f>
         <v>46.493732585853841</v>
       </c>
       <c r="H3" s="3">
-        <f t="shared" ref="H3:H8" si="2">IFERROR(B3/F3,)</f>
+        <f t="shared" ref="H3:H5" si="2">IFERROR(B3/F3,)</f>
         <v>84.271481594158814</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1118,7 +1039,7 @@
         <v>75.392443324937034</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -1147,163 +1068,122 @@
         <v>86.429871135446049</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="1">
-        <v>4708140</v>
+        <v>5159377.333333333</v>
       </c>
       <c r="C6" s="1">
-        <v>12928777</v>
+        <v>13507883.333333334</v>
       </c>
       <c r="D6" s="2">
         <f t="shared" si="0"/>
-        <v>0.63584026547909367</v>
+        <v>0.61804694295800111</v>
       </c>
       <c r="E6" s="1">
-        <v>102392</v>
+        <v>118313.66666666667</v>
       </c>
       <c r="F6" s="1">
-        <v>49916</v>
+        <v>59829</v>
       </c>
       <c r="G6" s="3">
-        <f t="shared" si="1"/>
-        <v>45.981521993905773</v>
+        <f t="shared" ref="G6" si="3">IFERROR(B6/E6,)</f>
+        <v>43.60761929447429</v>
       </c>
       <c r="H6" s="3">
-        <f t="shared" si="2"/>
-        <v>94.321259716323425</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+        <f t="shared" ref="H6" si="4">IFERROR(B6/F6,)</f>
+        <v>86.235393092535944</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="1">
-        <v>5190567</v>
+        <v>6000950</v>
       </c>
       <c r="C7" s="1">
-        <v>13084044</v>
+        <v>14850434</v>
       </c>
       <c r="D7" s="2">
         <f t="shared" si="0"/>
-        <v>0.60329031299497315</v>
+        <v>0.59590743273900282</v>
       </c>
       <c r="E7" s="1">
-        <v>118891</v>
-      </c>
-      <c r="F7" s="1">
-        <v>61861</v>
+        <v>88216</v>
+      </c>
+      <c r="F7">
+        <v>60948</v>
       </c>
       <c r="G7" s="3">
-        <f t="shared" si="1"/>
-        <v>43.658199527298116</v>
+        <f t="shared" ref="G7" si="5">IFERROR(B7/E7,)</f>
+        <v>68.025641606964726</v>
       </c>
       <c r="H7" s="3">
-        <f t="shared" si="2"/>
-        <v>83.906936518969943</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="1">
-        <v>5000354</v>
-      </c>
-      <c r="C8" s="1">
-        <v>12347958</v>
-      </c>
-      <c r="D8" s="2">
-        <f t="shared" si="0"/>
-        <v>0.59504607968378254</v>
-      </c>
-      <c r="E8" s="1">
-        <v>102595</v>
-      </c>
-      <c r="F8">
-        <v>61104</v>
-      </c>
-      <c r="G8" s="3">
-        <f t="shared" si="1"/>
-        <v>48.738768945855064</v>
-      </c>
-      <c r="H8" s="3">
-        <f t="shared" si="2"/>
-        <v>81.833496988740507</v>
-      </c>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13"/>
-      <c r="N8" s="13"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="1"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+        <f t="shared" ref="H7" si="6">IFERROR(B7/F7,)</f>
+        <v>98.460162761698498</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="L11" s="8"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="L12" s="9"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="1"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="L13" s="9"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
-      <c r="L14" s="8"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="L15" s="9"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="1"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="L16" s="9"/>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="L17" s="9"/>
+      <c r="L14" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="M8:N8"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAA9AD5E-B5CB-413A-ABB0-6907D8565D10}">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="2" max="2" width="8.90625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.90625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
@@ -1372,7 +1252,7 @@
         <v>10408805</v>
       </c>
       <c r="D3" s="2">
-        <f t="shared" ref="D3:D8" si="0">IFERROR(1-B3/C3,)</f>
+        <f t="shared" ref="D3:D7" si="0">IFERROR(1-B3/C3,)</f>
         <v>0.70936442752073847</v>
       </c>
       <c r="E3" s="1">
@@ -1382,11 +1262,11 @@
         <v>85945</v>
       </c>
       <c r="G3" s="3">
-        <f t="shared" ref="G3:G8" si="1">IFERROR(B3/E3,)</f>
+        <f t="shared" ref="G3:G5" si="1">IFERROR(B3/E3,)</f>
         <v>21.837014740063811</v>
       </c>
       <c r="H3" s="3">
-        <f t="shared" ref="H3:H8" si="2">IFERROR(B3/F3,)</f>
+        <f t="shared" ref="H3:H5" si="2">IFERROR(B3/F3,)</f>
         <v>35.198894641922159</v>
       </c>
     </row>
@@ -1453,28 +1333,28 @@
         <v>12</v>
       </c>
       <c r="B6" s="1">
-        <v>2335195</v>
+        <v>1950089</v>
       </c>
       <c r="C6" s="1">
-        <v>7180216</v>
+        <v>6595346</v>
       </c>
       <c r="D6" s="2">
         <f t="shared" si="0"/>
-        <v>0.67477371154293964</v>
+        <v>0.70432347294592279</v>
       </c>
       <c r="E6" s="1">
-        <v>101590</v>
+        <v>91042.666666666672</v>
       </c>
       <c r="F6" s="1">
-        <v>71507</v>
+        <v>58911.666666666664</v>
       </c>
       <c r="G6" s="3">
-        <f t="shared" si="1"/>
-        <v>22.98646520326804</v>
+        <f t="shared" ref="G6" si="3">IFERROR(B6/E6,)</f>
+        <v>21.419506604961775</v>
       </c>
       <c r="H6" s="3">
-        <f t="shared" si="2"/>
-        <v>32.656872753716421</v>
+        <f t="shared" ref="H6" si="4">IFERROR(B6/F6,)</f>
+        <v>33.101915296913461</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -1482,63 +1362,29 @@
         <v>13</v>
       </c>
       <c r="B7" s="1">
-        <v>2154828</v>
+        <v>2925953</v>
       </c>
       <c r="C7" s="1">
-        <v>6954990</v>
+        <v>8484740</v>
       </c>
       <c r="D7" s="2">
         <f t="shared" si="0"/>
-        <v>0.69017525546406255</v>
-      </c>
-      <c r="E7" s="1">
-        <v>95534</v>
+        <v>0.65515113014659265</v>
+      </c>
+      <c r="E7" s="12">
+        <v>106863</v>
       </c>
       <c r="F7" s="1">
-        <v>62556</v>
+        <v>70949</v>
       </c>
       <c r="G7" s="3">
-        <f t="shared" si="1"/>
-        <v>22.555613708208597</v>
+        <f t="shared" ref="G7" si="5">IFERROR(B7/E7,)</f>
+        <v>27.380412303603681</v>
       </c>
       <c r="H7" s="3">
-        <f t="shared" si="2"/>
-        <v>34.446384039900252</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="1">
-        <v>924003</v>
-      </c>
-      <c r="C8" s="1">
-        <v>3830831</v>
-      </c>
-      <c r="D8" s="2">
-        <f t="shared" si="0"/>
-        <v>0.75879828684690087</v>
-      </c>
-      <c r="E8" s="1">
-        <v>58893</v>
-      </c>
-      <c r="F8">
-        <v>34468</v>
-      </c>
-      <c r="G8" s="3">
-        <f t="shared" si="1"/>
-        <v>15.689521674901941</v>
-      </c>
-      <c r="H8" s="3">
-        <f t="shared" si="2"/>
-        <v>26.807560635952189</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="2"/>
+        <f t="shared" ref="H7" si="6">IFERROR(B7/F7,)</f>
+        <v>41.240228896813207</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1547,7 +1393,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A5EF3B8-A3DC-45F4-A95B-1BA7F1C29896}">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="9.90625" bestFit="1" customWidth="1"/>
@@ -1630,11 +1476,11 @@
         <v>189161</v>
       </c>
       <c r="G3" s="3">
-        <f t="shared" ref="G3:G8" si="0">IFERROR(B3/E3,)</f>
+        <f t="shared" ref="G3:G5" si="0">IFERROR(B3/E3,)</f>
         <v>32.937022698906304</v>
       </c>
       <c r="H3" s="3">
-        <f t="shared" ref="H3:H8" si="1">IFERROR(B3/F3,0)</f>
+        <f t="shared" ref="H3:H5" si="1">IFERROR(B3/F3,0)</f>
         <v>65.847230665940657</v>
       </c>
     </row>
@@ -1701,28 +1547,28 @@
         <v>12</v>
       </c>
       <c r="B6" s="1">
-        <v>10507488</v>
+        <v>10803366.666666666</v>
       </c>
       <c r="C6" s="1">
-        <v>33467089</v>
+        <v>34557213.333333336</v>
       </c>
       <c r="D6" s="2">
-        <f>IFERROR(1-B6/'Enterprise-Cars'!B16,0)</f>
-        <v>0</v>
+        <f t="shared" ref="D6:D7" si="2">IFERROR(1-B6/C6,0)</f>
+        <v>0.68737737726537373</v>
       </c>
       <c r="E6" s="1">
-        <v>302793</v>
+        <v>322469.33333333331</v>
       </c>
       <c r="F6" s="1">
-        <v>183811</v>
+        <v>199022.33333333334</v>
       </c>
       <c r="G6" s="3">
-        <f t="shared" si="0"/>
-        <v>34.701885446493151</v>
+        <f t="shared" ref="G6:G7" si="3">IFERROR(B6/E6,)</f>
+        <v>33.501997089128892</v>
       </c>
       <c r="H6" s="3">
-        <f t="shared" si="1"/>
-        <v>57.164631061253132</v>
+        <f t="shared" ref="H6:H7" si="4">IFERROR(B6/F6,0)</f>
+        <v>54.282182736610793</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -1730,59 +1576,29 @@
         <v>13</v>
       </c>
       <c r="B7" s="1">
-        <v>11521198</v>
+        <v>10800195</v>
       </c>
       <c r="C7" s="1">
-        <v>34170189</v>
+        <v>39703408</v>
       </c>
       <c r="D7" s="2">
-        <f>IFERROR(1-B7/'Enterprise-Cars'!C16,0)</f>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>0.72797813729239569</v>
       </c>
       <c r="E7" s="1">
-        <v>355617</v>
+        <v>291573</v>
       </c>
       <c r="F7" s="1">
-        <v>230542</v>
+        <v>178667</v>
       </c>
       <c r="G7" s="3">
-        <f t="shared" si="0"/>
-        <v>32.397770635262091</v>
+        <f t="shared" si="3"/>
+        <v>37.041135496085026</v>
       </c>
       <c r="H7" s="3">
-        <f t="shared" si="1"/>
-        <v>49.974399458666966</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="1">
-        <v>10381414</v>
-      </c>
-      <c r="D8" s="2">
-        <f>IFERROR(1-B8/C8,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="1">
-        <v>308998</v>
-      </c>
-      <c r="F8" s="1">
-        <v>182714</v>
-      </c>
-      <c r="G8" s="3">
-        <f t="shared" si="0"/>
-        <v>33.597026517970988</v>
-      </c>
-      <c r="H8" s="3">
-        <f t="shared" si="1"/>
-        <v>56.817835524371425</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C10" s="1"/>
-      <c r="D10" s="4"/>
+        <f t="shared" si="4"/>
+        <v>60.448739834440609</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1791,15 +1607,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{763F5313-635C-4516-969C-7DEC0B477EC2}">
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="3" width="8.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="8.90625" customWidth="1"/>
-    <col min="14" max="15" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="9.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1810,22 +1625,10 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1835,26 +1638,14 @@
       <c r="C2" s="1">
         <v>8563205.666666666</v>
       </c>
-      <c r="D2" s="1">
-        <v>87405.333329999994</v>
-      </c>
-      <c r="E2" s="1">
-        <v>60984.666669999999</v>
-      </c>
-      <c r="F2" s="2">
+      <c r="D2" s="2">
         <f>1-B2/C2</f>
         <v>0.51345533878531546</v>
       </c>
-      <c r="G2" s="12">
-        <f>B2/D2</f>
-        <v>47.667365837617361</v>
-      </c>
-      <c r="H2" s="3">
-        <f>B2/E2</f>
-        <v>68.318517219174296</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="E2" s="11"/>
+      <c r="F2" s="3"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1864,26 +1655,14 @@
       <c r="C3" s="1">
         <v>8672452.666666666</v>
       </c>
-      <c r="D3" s="1">
-        <v>51662.333330000001</v>
-      </c>
-      <c r="E3" s="1">
-        <v>37841</v>
-      </c>
-      <c r="F3" s="2">
+      <c r="D3" s="2">
         <f>1-B3/C3</f>
         <v>0.67360579041115543</v>
       </c>
-      <c r="G3" s="12">
-        <f t="shared" ref="G3:G8" si="0">B3/D3</f>
-        <v>54.791143776883942</v>
-      </c>
-      <c r="H3" s="3">
-        <f t="shared" ref="H3:H8" si="1">B3/E3</f>
-        <v>74.803475947605335</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="E3" s="11"/>
+      <c r="F3" s="3"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1893,28 +1672,16 @@
       <c r="C4" s="1">
         <v>7208672.666666667</v>
       </c>
-      <c r="D4" s="1">
-        <v>40684</v>
-      </c>
-      <c r="E4" s="1">
-        <v>26378.666669999999</v>
-      </c>
-      <c r="F4" s="2">
+      <c r="D4" s="2">
         <f>1-B4/C4</f>
         <v>0.68386662768892548</v>
       </c>
-      <c r="G4" s="12">
-        <f t="shared" si="0"/>
-        <v>56.014698653033136</v>
-      </c>
-      <c r="H4" s="3">
-        <f t="shared" si="1"/>
-        <v>86.391857045290152</v>
-      </c>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="E4" s="11"/>
+      <c r="F4" s="3"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -1924,147 +1691,69 @@
       <c r="C5" s="1">
         <v>7819269.333333333</v>
       </c>
-      <c r="D5" s="1">
-        <v>42768</v>
-      </c>
-      <c r="E5" s="1">
-        <v>31352.333330000001</v>
-      </c>
-      <c r="F5" s="2">
+      <c r="D5" s="2">
         <f>1-B5/C5</f>
         <v>0.6988098376455294</v>
       </c>
-      <c r="G5" s="12">
-        <f t="shared" si="0"/>
-        <v>55.066568462401797</v>
-      </c>
-      <c r="H5" s="3">
-        <f t="shared" si="1"/>
-        <v>75.116801521961875</v>
-      </c>
-      <c r="O5" s="1"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="E5" s="11"/>
+      <c r="F5" s="3"/>
+      <c r="M5" s="1"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="1">
-        <v>2063494</v>
+        <v>2798581.3333333335</v>
       </c>
       <c r="C6" s="1">
-        <v>7116075</v>
-      </c>
-      <c r="D6">
-        <v>45856</v>
-      </c>
-      <c r="E6">
-        <v>31951</v>
-      </c>
-      <c r="F6" s="2">
-        <f t="shared" ref="F6:F8" si="2">1-B6/C6</f>
-        <v>0.71002357338841993</v>
-      </c>
-      <c r="G6" s="12">
-        <f t="shared" si="0"/>
-        <v>44.999433007676203</v>
-      </c>
-      <c r="H6" s="3">
-        <f t="shared" si="1"/>
-        <v>64.583080341773339</v>
-      </c>
-      <c r="O6" s="1"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+        <v>8282686.666666667</v>
+      </c>
+      <c r="D6" s="2">
+        <f t="shared" ref="D6:D7" si="0">1-B6/C6</f>
+        <v>0.66211672058100302</v>
+      </c>
+      <c r="M6" s="1"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="1">
-        <v>3099524</v>
+        <v>3312566</v>
       </c>
       <c r="C7" s="1">
-        <v>7872299</v>
-      </c>
-      <c r="D7">
-        <v>61048</v>
-      </c>
-      <c r="E7">
-        <v>39385</v>
-      </c>
-      <c r="F7" s="2">
-        <f t="shared" si="2"/>
-        <v>0.60627460923422749</v>
-      </c>
-      <c r="G7" s="12">
-        <f t="shared" si="0"/>
-        <v>50.771917179923996</v>
-      </c>
-      <c r="H7" s="3">
-        <f t="shared" si="1"/>
-        <v>78.698083026532942</v>
-      </c>
-      <c r="O7" s="1"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="1">
-        <v>2500483</v>
-      </c>
-      <c r="C8">
-        <v>3814094</v>
-      </c>
-      <c r="D8">
-        <v>64898</v>
-      </c>
-      <c r="E8">
-        <v>39859</v>
-      </c>
-      <c r="F8" s="2">
-        <f t="shared" si="2"/>
-        <v>0.34440970778381441</v>
-      </c>
-      <c r="G8" s="12">
-        <f t="shared" si="0"/>
-        <v>38.529430799100126</v>
-      </c>
-      <c r="H8" s="3">
-        <f t="shared" si="1"/>
-        <v>62.733209563712087</v>
-      </c>
-      <c r="O8" s="1"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="O9" s="1"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="O10" s="1"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="O11" s="1"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="O12" s="1"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="O13" s="1"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="O14" s="1"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="O15" s="1"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="O16" s="1"/>
-    </row>
-    <row r="17" spans="14:15" x14ac:dyDescent="0.35">
-      <c r="O17" s="1"/>
-    </row>
-    <row r="18" spans="14:15" x14ac:dyDescent="0.35">
-      <c r="N18" s="1"/>
+        <v>9575633</v>
+      </c>
+      <c r="D7" s="2">
+        <f t="shared" si="0"/>
+        <v>0.65406297421799686</v>
+      </c>
+      <c r="M7" s="1"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="M8" s="1"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="M9" s="1"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="M10" s="1"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="M11" s="1"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="M12" s="1"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="M13" s="1"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="M14" s="1"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="L15" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2073,7 +1762,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26FE633C-9422-4872-865F-7200F0788355}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
@@ -2142,7 +1831,7 @@
         <v>2321980.6666666665</v>
       </c>
       <c r="D3" s="2">
-        <f t="shared" ref="D3:D8" si="0">IFERROR(1-B3/C3,)</f>
+        <f t="shared" ref="D3:D7" si="0">IFERROR(1-B3/C3,)</f>
         <v>0.67858388714692142</v>
       </c>
       <c r="E3">
@@ -2152,11 +1841,11 @@
         <v>14003.333333333334</v>
       </c>
       <c r="G3" s="3">
-        <f t="shared" ref="G3:G8" si="1">IFERROR(B3/E3,)</f>
+        <f t="shared" ref="G3:G5" si="1">IFERROR(B3/E3,)</f>
         <v>38.069883697204652</v>
       </c>
       <c r="H3" s="3">
-        <f t="shared" ref="H3:H8" si="2">IFERROR(B3/F3,)</f>
+        <f t="shared" ref="H3:H5" si="2">IFERROR(B3/F3,)</f>
         <v>53.296024756010475</v>
       </c>
     </row>
@@ -2223,28 +1912,28 @@
         <v>12</v>
       </c>
       <c r="B6">
-        <v>880294</v>
+        <v>860027.33333333337</v>
       </c>
       <c r="C6">
-        <v>1978185</v>
+        <v>2273250.3333333335</v>
       </c>
       <c r="D6" s="2">
         <f t="shared" si="0"/>
-        <v>0.55499915326422955</v>
+        <v>0.62167504356097458</v>
       </c>
       <c r="E6">
-        <v>21514</v>
+        <v>24020.333333333332</v>
       </c>
       <c r="F6">
-        <v>19254</v>
+        <v>20565.666666666668</v>
       </c>
       <c r="G6" s="3">
-        <f t="shared" si="1"/>
-        <v>40.917263177465834</v>
+        <f t="shared" ref="G6" si="3">IFERROR(B6/E6,)</f>
+        <v>35.804138160724946</v>
       </c>
       <c r="H6" s="3">
-        <f t="shared" si="2"/>
-        <v>45.720058169730962</v>
+        <f t="shared" ref="H6" si="4">IFERROR(B6/F6,)</f>
+        <v>41.818597338606416</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -2252,54 +1941,28 @@
         <v>13</v>
       </c>
       <c r="B7">
-        <v>750816</v>
+        <v>1441769</v>
       </c>
       <c r="C7">
-        <v>2006766</v>
+        <v>1609374</v>
       </c>
       <c r="D7" s="2">
         <f t="shared" si="0"/>
-        <v>0.62585772332200174</v>
+        <v>0.10414297733155875</v>
       </c>
       <c r="E7">
-        <v>22011</v>
+        <v>47356</v>
       </c>
       <c r="F7">
-        <v>20413</v>
+        <v>34161</v>
       </c>
       <c r="G7" s="3">
-        <f t="shared" si="1"/>
-        <v>34.11094452773613</v>
+        <f t="shared" ref="G7" si="5">IFERROR(B7/E7,)</f>
+        <v>30.445328997381537</v>
       </c>
       <c r="H7" s="3">
-        <f t="shared" si="2"/>
-        <v>36.781266839758977</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8">
-        <v>722657</v>
-      </c>
-      <c r="D8" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>20517</v>
-      </c>
-      <c r="F8">
-        <v>16843</v>
-      </c>
-      <c r="G8" s="3">
-        <f t="shared" si="1"/>
-        <v>35.222352195740115</v>
-      </c>
-      <c r="H8" s="3">
-        <f t="shared" si="2"/>
-        <v>42.905480021373862</v>
+        <f t="shared" ref="H7" si="6">IFERROR(B7/F7,)</f>
+        <v>42.205116946225225</v>
       </c>
     </row>
   </sheetData>
